--- a/Codigo/APIParametricos/wwwroot/plantillas/LayoutParametros.xlsx
+++ b/Codigo/APIParametricos/wwwroot/plantillas/LayoutParametros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITSSA\Proyectos\SapalParametricos\Codigo\APIParametricos\wwwroot\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1271D22A-5073-45D6-9248-B9E1BDE9459A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8403F8-A571-4C92-BC82-37630F88A6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7049BC8D-B486-4F1D-87AC-1429AFECAE49}"/>
   </bookViews>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Descripción</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Tipo de Obra</t>
   </si>
   <si>
-    <t>Tipo de Trabajo</t>
-  </si>
-  <si>
     <t>Tipo de Material</t>
   </si>
   <si>
@@ -45,13 +39,13 @@
     <t>Diámetro de Tubería</t>
   </si>
   <si>
-    <t>Excavación en</t>
-  </si>
-  <si>
-    <t>Precio por ml</t>
-  </si>
-  <si>
-    <t>Columna1</t>
+    <t>Línea de Trabajo</t>
+  </si>
+  <si>
+    <t>Excavación</t>
+  </si>
+  <si>
+    <t>Precio por m</t>
   </si>
 </sst>
 </file>
@@ -403,47 +397,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC79717E-9206-4C48-ADA5-E494701C7A7B}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
